--- a/2026/GaiGene - Master.xlsx
+++ b/2026/GaiGene - Master.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="500" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1EE479F-3F84-479E-80C3-377089DF24BE}"/>
+  <xr:revisionPtr revIDLastSave="565" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BCFB3D9-0DC7-4287-A8E4-5782C56C1619}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="157">
   <si>
     <t>Date Ordered</t>
   </si>
@@ -214,6 +214,18 @@
     <t>eSun PLA-Lite Yellow filament</t>
   </si>
   <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan $100 </t>
+  </si>
+  <si>
+    <t>to pad the Capital One Checking Acct</t>
+  </si>
+  <si>
+    <t>Loan</t>
+  </si>
+  <si>
     <t>key rings</t>
   </si>
   <si>
@@ -238,7 +250,46 @@
     <t>Travel</t>
   </si>
   <si>
+    <t>Pacific</t>
+  </si>
+  <si>
+    <t>2 bee sets, collect $12</t>
+  </si>
+  <si>
+    <t>3 bee sets (24 bees)</t>
+  </si>
+  <si>
     <t>Business Meeting (2 bee sets, collect $12)</t>
+  </si>
+  <si>
+    <t>2 bee sets $8</t>
+  </si>
+  <si>
+    <t>2 bee sets (16 bees)</t>
+  </si>
+  <si>
+    <t>Business Meeting (1 bee sets, Musubee, ShinoBee, collect $8+$2credit)</t>
+  </si>
+  <si>
+    <t>1 bee set, 10 Musubee, 10 ShinoBee</t>
+  </si>
+  <si>
+    <t>1 bee set (8), and 10 Musubee and 10 ShinoBee - 28 bees</t>
+  </si>
+  <si>
+    <t>Business Meeting (1 bee sample, collect $14-$2=$12, all paid)</t>
+  </si>
+  <si>
+    <t>Deposit</t>
+  </si>
+  <si>
+    <t>$34 from Pacific -$1 for first dollar earned to replace initial $1 setup</t>
+  </si>
+  <si>
+    <t>first bank deposit (no expense or income, just document)</t>
+  </si>
+  <si>
+    <t>Document</t>
   </si>
   <si>
     <t>Date Contact</t>
@@ -490,7 +541,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +561,12 @@
       <sz val="12"/>
       <color rgb="FF444444"/>
       <name val="-Apple-System"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -534,7 +591,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -551,6 +608,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -866,13 +924,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
     <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="54.42578125" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1314,7 +1372,7 @@
         <v>16.216182</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="60.75">
+    <row r="17" spans="1:14" ht="60.75">
       <c r="A17" s="4">
         <v>46088</v>
       </c>
@@ -1342,7 +1400,7 @@
         <v>10.807182000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="106.5">
+    <row r="18" spans="1:14" ht="106.5">
       <c r="A18" s="4">
         <v>46102</v>
       </c>
@@ -1370,7 +1428,7 @@
         <v>29.143692000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19" s="4">
         <v>46102</v>
       </c>
@@ -1398,7 +1456,7 @@
         <v>66.790332000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20" s="4">
         <v>46102</v>
       </c>
@@ -1426,7 +1484,7 @@
         <v>10.807182000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21" s="4">
         <v>46113</v>
       </c>
@@ -1457,7 +1515,7 @@
         <v>19.461582</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22" s="4">
         <v>46113</v>
       </c>
@@ -1488,7 +1546,7 @@
         <v>10.807182000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:14">
       <c r="A23" s="4">
         <v>46171</v>
       </c>
@@ -1522,7 +1580,7 @@
         <v>14.733482</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:14">
       <c r="A24" s="4">
         <v>46171</v>
       </c>
@@ -1560,7 +1618,7 @@
         <v>1344.3197740000003</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:14">
       <c r="A25" s="4">
         <v>46177</v>
       </c>
@@ -1588,7 +1646,7 @@
       </c>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:13" ht="60.75">
+    <row r="26" spans="1:14" ht="60.75">
       <c r="A26" s="4">
         <v>46184</v>
       </c>
@@ -1611,15 +1669,15 @@
         <v>2.16</v>
       </c>
       <c r="K26" s="2">
-        <f t="shared" ref="K26:K34" si="0">H26*$M$1</f>
+        <f t="shared" ref="K26:K35" si="0">H26*$M$1</f>
         <v>5.0716000000000001</v>
       </c>
       <c r="L26" s="2">
-        <f t="shared" ref="L26:L47" si="1">H26+I26+K26+J26</f>
+        <f t="shared" ref="L26:L50" si="1">H26+I26+K26+J26</f>
         <v>69.2316</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="30.75">
+    <row r="27" spans="1:14" ht="30.75">
       <c r="A27" s="4">
         <v>46183</v>
       </c>
@@ -1647,7 +1705,7 @@
         <v>21.635999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:14">
       <c r="A28" s="4">
         <v>46184</v>
       </c>
@@ -1675,7 +1733,7 @@
         <v>21.625181999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:14">
       <c r="A29" s="4">
         <v>46184</v>
       </c>
@@ -1706,7 +1764,7 @@
         <v>11.855259999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:14">
       <c r="A30" s="4">
         <v>46199</v>
       </c>
@@ -1737,169 +1795,155 @@
         <v>14.646303999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:14">
       <c r="A31" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" t="s">
+        <v>60</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="N31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="4">
         <v>46212</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>11</v>
       </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" t="s">
         <v>30</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>26</v>
       </c>
-      <c r="H31">
+      <c r="H32">
         <v>9.99</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K32" s="2">
         <f t="shared" si="0"/>
         <v>0.81718199999999996</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L32" s="2">
         <f t="shared" si="1"/>
         <v>10.807182000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="4">
+    <row r="33" spans="1:14">
+      <c r="A33" s="4">
         <v>46212</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>11</v>
       </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" t="s">
         <v>26</v>
       </c>
-      <c r="H32">
+      <c r="H33">
         <v>5.97</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K33" s="2">
         <f t="shared" si="0"/>
         <v>0.48834599999999995</v>
       </c>
-      <c r="L32" s="2">
+      <c r="L33" s="2">
         <f t="shared" si="1"/>
         <v>6.4583459999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="4">
+    <row r="34" spans="1:14">
+      <c r="A34" s="4">
         <v>46212</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>11</v>
       </c>
-      <c r="C33" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" t="s">
         <v>26</v>
       </c>
-      <c r="H33">
+      <c r="H34">
         <v>4.8899999999999997</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K34" s="2">
         <f t="shared" si="0"/>
         <v>0.40000199999999997</v>
       </c>
-      <c r="L33" s="2">
+      <c r="L34" s="2">
         <f t="shared" si="1"/>
         <v>5.2900019999999994</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="4">
+    <row r="35" spans="1:14">
+      <c r="A35" s="4">
         <v>46212</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>11</v>
       </c>
-      <c r="C34" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" t="s">
         <v>30</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E35" t="s">
         <v>26</v>
       </c>
-      <c r="H34">
+      <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K35" s="2">
         <f t="shared" si="0"/>
         <v>0.81718199999999996</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L35" s="2">
         <f t="shared" si="1"/>
         <v>10.807182000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="4">
+    <row r="36" spans="1:14">
+      <c r="A36" s="4">
         <v>46222</v>
-      </c>
-      <c r="B35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E35" t="s">
-        <v>64</v>
-      </c>
-      <c r="F35">
-        <f>18.5*2</f>
-        <v>37</v>
-      </c>
-      <c r="G35">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="H35">
-        <f>F35*G35</f>
-        <v>26.824999999999999</v>
-      </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2">
-        <f t="shared" si="1"/>
-        <v>26.824999999999999</v>
-      </c>
-      <c r="M35" s="2">
-        <f>SUM(L2:L35)</f>
-        <v>1891.5018320000004</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="4">
-        <v>46229</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F36">
+        <f>18.5*2</f>
         <v>37</v>
       </c>
       <c r="G36">
@@ -1914,68 +1958,186 @@
         <f t="shared" si="1"/>
         <v>26.824999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="K37" s="2">
-        <f>H37*$M$1</f>
-        <v>0</v>
-      </c>
-      <c r="L37" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="K38" s="2">
-        <f>H38*$M$1</f>
-        <v>0</v>
-      </c>
+      <c r="M36" s="2">
+        <f>SUM(L2:L36)</f>
+        <v>1891.5018320000004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="4">
+        <v>46229</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" t="s">
+        <v>71</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="N37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="4">
+        <v>46229</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" t="s">
+        <v>68</v>
+      </c>
+      <c r="F38">
+        <v>37</v>
+      </c>
+      <c r="G38">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="H38">
+        <f>F38*G38</f>
+        <v>26.824999999999999</v>
+      </c>
+      <c r="K38" s="2"/>
       <c r="L38" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="K39" s="2">
-        <f>H39*$M$1</f>
-        <v>0</v>
-      </c>
-      <c r="L39" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="K40" s="2">
-        <f>H40*$M$1</f>
-        <v>0</v>
-      </c>
+        <f>H38+I38+K38+J38</f>
+        <v>26.824999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="4">
+        <v>46236</v>
+      </c>
+      <c r="B39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" t="s">
+        <v>74</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="N39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="4">
+        <v>46236</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="H40">
+        <f>F40*G40</f>
+        <v>26.824999999999999</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="L40" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>26.824999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="4">
+        <v>46241</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>77</v>
+      </c>
       <c r="K41" s="2">
         <f>H41*$M$1</f>
         <v>0</v>
       </c>
       <c r="L41" s="2">
-        <f t="shared" si="1"/>
+        <f>H41+I41+K41+J41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="K42" s="2">
-        <f>H42*$M$1</f>
-        <v>0</v>
-      </c>
+      <c r="N41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="4">
+        <v>46241</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42">
+        <v>37</v>
+      </c>
+      <c r="G42">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="H42">
+        <f>F42*G42</f>
+        <v>26.824999999999999</v>
+      </c>
+      <c r="K42" s="2"/>
       <c r="L42" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>26.824999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="4">
+        <v>46242</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" t="s">
+        <v>82</v>
+      </c>
       <c r="K43" s="2">
         <f>H43*$M$1</f>
         <v>0</v>
@@ -1985,7 +2147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:14">
       <c r="K44" s="2">
         <f>H44*$M$1</f>
         <v>0</v>
@@ -1995,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:14">
       <c r="K45" s="2">
         <f>H45*$M$1</f>
         <v>0</v>
@@ -2005,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:14">
       <c r="K46" s="2">
         <f>H46*$M$1</f>
         <v>0</v>
@@ -2015,12 +2177,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:14">
       <c r="K47" s="2">
         <f>H47*$M$1</f>
         <v>0</v>
       </c>
       <c r="L47" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="K48" s="2">
+        <f>H48*$M$1</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="11:12">
+      <c r="K49" s="2">
+        <f>H49*$M$1</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="11:12">
+      <c r="K50" s="2">
+        <f>H50*$M$1</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2043,34 +2235,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="G1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2078,7 +2270,7 @@
         <v>46224</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G2">
         <v>0.5</v>
@@ -2092,18 +2284,18 @@
     </row>
     <row r="3" spans="1:10">
       <c r="B3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="B4" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2126,30 +2318,30 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>2606</v>
@@ -2165,10 +2357,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>2606</v>
@@ -2184,10 +2376,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>2606</v>
@@ -2203,10 +2395,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C5">
         <v>2606</v>
@@ -2222,10 +2414,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>2606</v>
@@ -2241,10 +2433,10 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C7">
         <v>2606</v>
@@ -2260,16 +2452,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>2606</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="1"/>
@@ -2282,16 +2474,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>2606</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="1"/>
@@ -2323,31 +2515,31 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="G1" t="s">
         <v>10</v>
       </c>
       <c r="AA1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AB1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -2355,13 +2547,13 @@
         <v>46184</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -2374,16 +2566,16 @@
         <v>2</v>
       </c>
       <c r="AA2" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AB2" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AC2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AD2" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="30.75">
@@ -2391,13 +2583,13 @@
         <v>46184</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -2410,16 +2602,16 @@
         <v>2</v>
       </c>
       <c r="AA3" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AB3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AC3" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="AD3" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="30.75">
@@ -2427,13 +2619,13 @@
         <v>46184</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -2446,10 +2638,10 @@
         <v>2</v>
       </c>
       <c r="AA4" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -2457,13 +2649,13 @@
         <v>46184</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2481,13 +2673,13 @@
         <v>46184</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -2505,13 +2697,13 @@
         <v>46184</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -2529,13 +2721,13 @@
         <v>46184</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -2553,13 +2745,13 @@
         <v>46184</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -2611,90 +2803,90 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="G1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="336">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
         <v>51</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="137.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45.75">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
